--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PISCAS - 18_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PISCAS - 18_01.xlsx
@@ -2011,7 +2011,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PISCAS - 18_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PISCAS - 18_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PISCA COMPLETO PROTORK DT NXR150 BROS 2013 A 2014/ BROS NXR160 2015 A 2018</t>
+          <t>PISCA COMPLETO PROTORK D T NXR150 BROS 2013 A 2014/ BROS NXR160 2015 A 2018</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,7 +572,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -604,7 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -625,7 +612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -646,7 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -667,7 +652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -688,7 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -730,7 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -751,7 +732,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -772,7 +752,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -793,7 +772,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -814,7 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -835,7 +812,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -856,7 +832,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -877,7 +852,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -898,7 +872,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -919,7 +892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -940,7 +912,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -961,7 +932,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -982,7 +952,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1003,7 +972,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1024,7 +992,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1045,7 +1012,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1066,7 +1032,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1087,7 +1052,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1108,7 +1072,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1129,7 +1092,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1150,7 +1112,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1171,7 +1132,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1192,7 +1152,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1213,7 +1172,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1234,7 +1192,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1255,7 +1212,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1276,7 +1232,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1297,7 +1252,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1318,7 +1272,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1339,7 +1292,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1360,7 +1312,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1381,7 +1332,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1402,7 +1352,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1423,7 +1372,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1444,7 +1392,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1465,7 +1412,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1486,7 +1432,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1507,7 +1452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1528,7 +1472,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1549,7 +1492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1570,7 +1512,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1591,7 +1532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1612,7 +1552,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1633,7 +1572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1654,7 +1592,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1675,7 +1612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1696,7 +1632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1717,7 +1652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1738,7 +1672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1759,7 +1692,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1780,7 +1712,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1801,7 +1732,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1822,7 +1752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1843,7 +1772,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1864,7 +1792,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1885,7 +1812,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1906,7 +1832,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1927,7 +1852,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1948,7 +1872,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1969,7 +1892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1990,7 +1912,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2011,11 +1932,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2036,7 +1952,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2057,7 +1972,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2074,7 +1988,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2095,7 +2008,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2116,7 +2028,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2137,7 +2048,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2158,7 +2068,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2179,7 +2088,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2200,7 +2108,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2221,7 +2128,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2238,7 +2144,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2259,7 +2164,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2280,7 +2184,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2301,11 +2204,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2326,11 +2224,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2351,11 +2244,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2376,7 +2264,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2397,7 +2284,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2418,7 +2304,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2439,7 +2324,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2460,7 +2344,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2481,7 +2364,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2502,7 +2384,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2523,7 +2404,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2544,7 +2424,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2565,11 +2444,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2590,7 +2464,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2611,11 +2484,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2636,7 +2504,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2657,7 +2524,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2678,7 +2544,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2695,7 +2560,6 @@
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2708,7 +2572,6 @@
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
